--- a/dist/SUBMISSION_FINAL/P7_Capstone_JIBS/p7_capstone_jibs_replication_data.xlsx
+++ b/dist/SUBMISSION_FINAL/P7_Capstone_JIBS/p7_capstone_jibs_replication_data.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Regression_Coefficients" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Turning_Points" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Robustness" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Figures_Embedded" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +49,25 @@
     <font>
       <b val="1"/>
       <i val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00305496"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -80,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -91,6 +111,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -165,6 +191,61 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="3552825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5715000" cy="2247900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -590,7 +671,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1371,7 +1451,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1516,17 +1595,6 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1563,19 +1631,8 @@
         <v>0.0001</v>
       </c>
       <c r="J5" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1600,7 +1657,6 @@
       <c r="F6" t="n">
         <v>0.3822</v>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>8253</v>
       </c>
@@ -1608,19 +1664,8 @@
         <v>0.0001</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1659,7 +1704,6 @@
       <c r="J7" t="n">
         <v>0.175</v>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>-13.36709726482501</v>
       </c>
@@ -1674,12 +1718,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1718,7 +1756,6 @@
       <c r="J8" t="n">
         <v>0.175</v>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>-13.36709726482501</v>
       </c>
@@ -1733,12 +1770,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1777,7 +1808,6 @@
       <c r="J9" t="n">
         <v>0.175</v>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>-13.36709726482501</v>
       </c>
@@ -1792,12 +1822,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1836,7 +1860,6 @@
       <c r="J10" t="n">
         <v>0.1836</v>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>-13.68182130929589</v>
       </c>
@@ -1851,12 +1874,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1895,7 +1912,6 @@
       <c r="J11" t="n">
         <v>0.1836</v>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>-13.68182130929589</v>
       </c>
@@ -1910,12 +1926,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1954,7 +1964,6 @@
       <c r="J12" t="n">
         <v>0.1836</v>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
         <v>-13.68182130929589</v>
       </c>
@@ -1969,12 +1978,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2013,7 +2016,6 @@
       <c r="J13" t="n">
         <v>0.1836</v>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>-13.68182130929589</v>
       </c>
@@ -2028,12 +2030,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2072,7 +2068,6 @@
       <c r="J14" t="n">
         <v>0.1836</v>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
         <v>-13.68182130929589</v>
       </c>
@@ -2087,12 +2082,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2131,7 +2120,6 @@
       <c r="J15" t="n">
         <v>0.1836</v>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>-13.68182130929589</v>
       </c>
@@ -2146,12 +2134,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2213,10 +2195,6 @@
       <c r="Q16" t="n">
         <v>5.39</v>
       </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2278,10 +2256,6 @@
       <c r="Q17" t="n">
         <v>5.39</v>
       </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2343,10 +2317,6 @@
       <c r="Q18" t="n">
         <v>5.39</v>
       </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2408,10 +2378,6 @@
       <c r="Q19" t="n">
         <v>5.39</v>
       </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2473,10 +2439,6 @@
       <c r="Q20" t="n">
         <v>5.39</v>
       </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2538,10 +2500,6 @@
       <c r="Q21" t="n">
         <v>5.39</v>
       </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2603,10 +2561,6 @@
       <c r="Q22" t="n">
         <v>5.39</v>
       </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2668,10 +2622,6 @@
       <c r="Q23" t="n">
         <v>5.39</v>
       </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2733,10 +2683,6 @@
       <c r="Q24" t="n">
         <v>5.39</v>
       </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2798,10 +2744,6 @@
       <c r="Q25" t="n">
         <v>5.39</v>
       </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2863,10 +2805,6 @@
       <c r="Q26" t="n">
         <v>5.39</v>
       </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2905,7 +2843,6 @@
       <c r="J27" t="n">
         <v>0.2047</v>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
         <v>-12.56632388004711</v>
       </c>
@@ -2920,12 +2857,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2964,7 +2895,6 @@
       <c r="J28" t="n">
         <v>0.2047</v>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
         <v>-12.56632388004711</v>
       </c>
@@ -2979,12 +2909,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3023,7 +2947,6 @@
       <c r="J29" t="n">
         <v>0.2047</v>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
         <v>-12.56632388004711</v>
       </c>
@@ -3038,12 +2961,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3082,7 +2999,6 @@
       <c r="J30" t="n">
         <v>0.2047</v>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
         <v>-12.56632388004711</v>
       </c>
@@ -3097,12 +3013,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3141,7 +3051,6 @@
       <c r="J31" t="n">
         <v>0.2047</v>
       </c>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
         <v>-12.56632388004711</v>
       </c>
@@ -3156,12 +3065,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3200,7 +3103,6 @@
       <c r="J32" t="n">
         <v>0.2047</v>
       </c>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
         <v>-12.56632388004711</v>
       </c>
@@ -3215,12 +3117,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3259,7 +3155,6 @@
       <c r="J33" t="n">
         <v>0.2047</v>
       </c>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
         <v>-12.56632388004711</v>
       </c>
@@ -3274,12 +3169,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3318,7 +3207,6 @@
       <c r="J34" t="n">
         <v>0.235</v>
       </c>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
         <v>-13.21480688116424</v>
       </c>
@@ -3333,16 +3221,12 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="n">
         <v>109.7217</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3381,7 +3265,6 @@
       <c r="J35" t="n">
         <v>0.235</v>
       </c>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
         <v>-13.21480688116424</v>
       </c>
@@ -3396,16 +3279,12 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="n">
         <v>109.7217</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3444,7 +3323,6 @@
       <c r="J36" t="n">
         <v>0.235</v>
       </c>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
         <v>-13.21480688116424</v>
       </c>
@@ -3459,16 +3337,12 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="n">
         <v>109.7217</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3493,7 +3367,6 @@
       <c r="F37" t="n">
         <v>0.5409</v>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>8224</v>
       </c>
@@ -3503,7 +3376,6 @@
       <c r="J37" t="n">
         <v>0.235</v>
       </c>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
         <v>-13.21480688116424</v>
       </c>
@@ -3518,16 +3390,12 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="n">
         <v>109.7217</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3566,7 +3434,6 @@
       <c r="J38" t="n">
         <v>0.235</v>
       </c>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
         <v>-13.21480688116424</v>
       </c>
@@ -3581,16 +3448,12 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="n">
         <v>109.7217</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3629,7 +3492,6 @@
       <c r="J39" t="n">
         <v>0.235</v>
       </c>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
         <v>-13.21480688116424</v>
       </c>
@@ -3644,16 +3506,12 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
         <v>109.7217</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3692,7 +3550,6 @@
       <c r="J40" t="n">
         <v>0.235</v>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
         <v>-13.21480688116424</v>
       </c>
@@ -3707,16 +3564,12 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="n">
         <v>109.7217</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3755,7 +3608,6 @@
       <c r="J41" t="n">
         <v>0.235</v>
       </c>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
         <v>-13.21480688116424</v>
       </c>
@@ -3770,16 +3622,12 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="n">
         <v>109.7217</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3818,7 +3666,6 @@
       <c r="J42" t="n">
         <v>0.235</v>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
         <v>-13.21480688116424</v>
       </c>
@@ -3833,16 +3680,12 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="n">
         <v>109.7217</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
       </c>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3881,7 +3724,6 @@
       <c r="J43" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -3896,10 +3738,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
       <c r="T43" t="n">
         <v>1.5818</v>
       </c>
@@ -3944,7 +3782,6 @@
       <c r="J44" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -3959,10 +3796,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
       <c r="T44" t="n">
         <v>1.5818</v>
       </c>
@@ -4007,7 +3840,6 @@
       <c r="J45" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -4022,10 +3854,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
       <c r="T45" t="n">
         <v>1.5818</v>
       </c>
@@ -4056,7 +3884,6 @@
       <c r="F46" t="n">
         <v>0.3468</v>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>8220</v>
       </c>
@@ -4066,7 +3893,6 @@
       <c r="J46" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -4081,10 +3907,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
       <c r="T46" t="n">
         <v>1.5818</v>
       </c>
@@ -4129,7 +3951,6 @@
       <c r="J47" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -4144,10 +3965,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
       <c r="T47" t="n">
         <v>1.5818</v>
       </c>
@@ -4192,7 +4009,6 @@
       <c r="J48" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -4207,10 +4023,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
       <c r="T48" t="n">
         <v>1.5818</v>
       </c>
@@ -4255,7 +4067,6 @@
       <c r="J49" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -4270,10 +4081,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
       <c r="T49" t="n">
         <v>1.5818</v>
       </c>
@@ -4318,7 +4125,6 @@
       <c r="J50" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K50" t="inlineStr"/>
       <c r="L50" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -4333,10 +4139,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
       <c r="T50" t="n">
         <v>1.5818</v>
       </c>
@@ -4381,7 +4183,6 @@
       <c r="J51" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -4396,10 +4197,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
       <c r="T51" t="n">
         <v>1.5818</v>
       </c>
@@ -4444,7 +4241,6 @@
       <c r="J52" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -4459,10 +4255,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
       <c r="T52" t="n">
         <v>1.5818</v>
       </c>
@@ -4507,7 +4299,6 @@
       <c r="J53" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -4522,10 +4313,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
       <c r="T53" t="n">
         <v>1.5818</v>
       </c>
@@ -4570,7 +4357,6 @@
       <c r="J54" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K54" t="inlineStr"/>
       <c r="L54" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -4585,10 +4371,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
       <c r="T54" t="n">
         <v>1.5818</v>
       </c>
@@ -4633,7 +4415,6 @@
       <c r="J55" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K55" t="inlineStr"/>
       <c r="L55" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -4648,12 +4429,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4692,7 +4467,6 @@
       <c r="J56" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -4707,12 +4481,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4751,7 +4519,6 @@
       <c r="J57" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -4766,12 +4533,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4796,7 +4557,6 @@
       <c r="F58" t="n">
         <v>0.2246</v>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>8220</v>
       </c>
@@ -4806,7 +4566,6 @@
       <c r="J58" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K58" t="inlineStr"/>
       <c r="L58" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -4821,12 +4580,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4865,7 +4618,6 @@
       <c r="J59" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -4880,12 +4632,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4924,7 +4670,6 @@
       <c r="J60" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K60" t="inlineStr"/>
       <c r="L60" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -4939,12 +4684,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4983,7 +4722,6 @@
       <c r="J61" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -4998,12 +4736,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5028,7 +4760,6 @@
       <c r="F62" t="n">
         <v>0.1254</v>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>8220</v>
       </c>
@@ -5038,7 +4769,6 @@
       <c r="J62" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -5053,12 +4783,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5083,7 +4807,6 @@
       <c r="F63" t="n">
         <v>0.1026</v>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>8220</v>
       </c>
@@ -5093,7 +4816,6 @@
       <c r="J63" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -5108,12 +4830,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5152,7 +4868,6 @@
       <c r="J64" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K64" t="inlineStr"/>
       <c r="L64" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -5167,12 +4882,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5211,7 +4920,6 @@
       <c r="J65" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K65" t="inlineStr"/>
       <c r="L65" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -5226,12 +4934,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5270,7 +4972,6 @@
       <c r="J66" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K66" t="inlineStr"/>
       <c r="L66" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -5285,12 +4986,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5329,7 +5024,6 @@
       <c r="J67" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K67" t="inlineStr"/>
       <c r="L67" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -5344,12 +5038,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5374,7 +5062,6 @@
       <c r="F68" t="n">
         <v>0.191</v>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>8220</v>
       </c>
@@ -5384,7 +5071,6 @@
       <c r="J68" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -5399,12 +5085,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5466,10 +5146,6 @@
       <c r="Q69" t="n">
         <v>1.48</v>
       </c>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5531,10 +5207,6 @@
       <c r="Q70" t="n">
         <v>1.48</v>
       </c>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5596,10 +5268,6 @@
       <c r="Q71" t="n">
         <v>1.48</v>
       </c>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5661,10 +5329,6 @@
       <c r="Q72" t="n">
         <v>1.48</v>
       </c>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5689,7 +5353,6 @@
       <c r="F73" t="n">
         <v>0.2971</v>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>8220</v>
       </c>
@@ -5722,10 +5385,6 @@
       <c r="Q73" t="n">
         <v>1.48</v>
       </c>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5787,10 +5446,6 @@
       <c r="Q74" t="n">
         <v>1.48</v>
       </c>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5852,10 +5507,6 @@
       <c r="Q75" t="n">
         <v>1.48</v>
       </c>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5917,10 +5568,6 @@
       <c r="Q76" t="n">
         <v>1.48</v>
       </c>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5982,10 +5629,6 @@
       <c r="Q77" t="n">
         <v>1.48</v>
       </c>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6010,7 +5653,6 @@
       <c r="F78" t="n">
         <v>0.9437</v>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>8220</v>
       </c>
@@ -6043,10 +5685,6 @@
       <c r="Q78" t="n">
         <v>1.48</v>
       </c>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6108,10 +5746,6 @@
       <c r="Q79" t="n">
         <v>1.48</v>
       </c>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6150,7 +5784,6 @@
       <c r="J80" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K80" t="inlineStr"/>
       <c r="L80" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -6165,12 +5798,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6195,7 +5822,6 @@
       <c r="F81" t="n">
         <v>0.1396</v>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>8220</v>
       </c>
@@ -6205,7 +5831,6 @@
       <c r="J81" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K81" t="inlineStr"/>
       <c r="L81" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -6220,12 +5845,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6264,7 +5883,6 @@
       <c r="J82" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K82" t="inlineStr"/>
       <c r="L82" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -6279,12 +5897,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6323,7 +5935,6 @@
       <c r="J83" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K83" t="inlineStr"/>
       <c r="L83" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -6338,12 +5949,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6382,7 +5987,6 @@
       <c r="J84" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K84" t="inlineStr"/>
       <c r="L84" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -6397,12 +6001,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6441,7 +6039,6 @@
       <c r="J85" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K85" t="inlineStr"/>
       <c r="L85" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -6456,12 +6053,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6500,7 +6091,6 @@
       <c r="J86" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K86" t="inlineStr"/>
       <c r="L86" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -6515,12 +6105,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6545,7 +6129,6 @@
       <c r="F87" t="n">
         <v>0.15</v>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>8220</v>
       </c>
@@ -6555,7 +6138,6 @@
       <c r="J87" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K87" t="inlineStr"/>
       <c r="L87" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -6570,12 +6152,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6614,7 +6190,6 @@
       <c r="J88" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K88" t="inlineStr"/>
       <c r="L88" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -6629,12 +6204,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6659,7 +6228,6 @@
       <c r="F89" t="n">
         <v>0.2115</v>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>8220</v>
       </c>
@@ -6669,7 +6237,6 @@
       <c r="J89" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K89" t="inlineStr"/>
       <c r="L89" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -6684,12 +6251,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6728,7 +6289,6 @@
       <c r="J90" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K90" t="inlineStr"/>
       <c r="L90" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -6743,12 +6303,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr"/>
-      <c r="U90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6773,7 +6327,6 @@
       <c r="F91" t="n">
         <v>0.3293</v>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>8220</v>
       </c>
@@ -6783,7 +6336,6 @@
       <c r="J91" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K91" t="inlineStr"/>
       <c r="L91" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -6798,12 +6350,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr"/>
-      <c r="U91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6842,7 +6388,6 @@
       <c r="J92" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K92" t="inlineStr"/>
       <c r="L92" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -6857,12 +6402,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
-      <c r="U92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6887,7 +6426,6 @@
       <c r="F93" t="n">
         <v>0.2191</v>
       </c>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>8220</v>
       </c>
@@ -6897,7 +6435,6 @@
       <c r="J93" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K93" t="inlineStr"/>
       <c r="L93" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -6912,12 +6449,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
-      <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6956,7 +6487,6 @@
       <c r="J94" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K94" t="inlineStr"/>
       <c r="L94" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -6971,12 +6501,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr"/>
-      <c r="U94" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7010,7 +6534,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -7585,11 +7108,6 @@
       <c r="E5" t="n">
         <v>45628.54</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7604,16 +7122,11 @@
         <v>0.0001</v>
       </c>
       <c r="D6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>45629.74</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7633,7 +7146,6 @@
       <c r="E7" t="n">
         <v>44043.32</v>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>1</v>
       </c>
@@ -7642,8 +7154,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7663,7 +7173,6 @@
       <c r="E8" t="n">
         <v>43831.6</v>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>1</v>
       </c>
@@ -7672,8 +7181,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7704,8 +7211,6 @@
           <t>inverted-U</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7725,7 +7230,6 @@
       <c r="E10" t="n">
         <v>43587.09</v>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>1</v>
       </c>
@@ -7734,8 +7238,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7755,7 +7257,6 @@
       <c r="E11" t="n">
         <v>43269.21</v>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>1</v>
       </c>
@@ -7767,7 +7268,6 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7787,7 +7287,6 @@
       <c r="E12" t="n">
         <v>43161.82</v>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>1</v>
       </c>
@@ -7796,7 +7295,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
         <v>0.2057</v>
       </c>
@@ -7819,7 +7317,6 @@
       <c r="E13" t="n">
         <v>43101.91</v>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
         <v>1</v>
       </c>
@@ -7828,8 +7325,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7860,8 +7355,6 @@
           <t>inverted-U</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7881,7 +7374,6 @@
       <c r="E15" t="n">
         <v>37152.3</v>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
         <v>1</v>
       </c>
@@ -7890,8 +7382,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -8044,17 +7534,6 @@
       <c r="J20" t="n">
         <v>0</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8091,19 +7570,8 @@
         <v>0.0001</v>
       </c>
       <c r="J21" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8128,7 +7596,6 @@
       <c r="F22" t="n">
         <v>0.3822</v>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>8253</v>
       </c>
@@ -8136,19 +7603,8 @@
         <v>0.0001</v>
       </c>
       <c r="J22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8187,7 +7643,6 @@
       <c r="J23" t="n">
         <v>0.175</v>
       </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
         <v>-13.36709726482501</v>
       </c>
@@ -8202,12 +7657,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8246,7 +7695,6 @@
       <c r="J24" t="n">
         <v>0.175</v>
       </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
         <v>-13.36709726482501</v>
       </c>
@@ -8261,12 +7709,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8305,7 +7747,6 @@
       <c r="J25" t="n">
         <v>0.175</v>
       </c>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
         <v>-13.36709726482501</v>
       </c>
@@ -8320,12 +7761,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8364,7 +7799,6 @@
       <c r="J26" t="n">
         <v>0.1836</v>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
         <v>-13.68182130929589</v>
       </c>
@@ -8379,12 +7813,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8423,7 +7851,6 @@
       <c r="J27" t="n">
         <v>0.1836</v>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
         <v>-13.68182130929589</v>
       </c>
@@ -8438,12 +7865,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8482,7 +7903,6 @@
       <c r="J28" t="n">
         <v>0.1836</v>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
         <v>-13.68182130929589</v>
       </c>
@@ -8497,12 +7917,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8564,10 +7978,6 @@
       <c r="Q29" t="n">
         <v>5.39</v>
       </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8629,10 +8039,6 @@
       <c r="Q30" t="n">
         <v>5.39</v>
       </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8694,10 +8100,6 @@
       <c r="Q31" t="n">
         <v>5.39</v>
       </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8736,7 +8138,6 @@
       <c r="J32" t="n">
         <v>0.2047</v>
       </c>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
         <v>-12.56632388004711</v>
       </c>
@@ -8751,12 +8152,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8795,7 +8190,6 @@
       <c r="J33" t="n">
         <v>0.2047</v>
       </c>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
         <v>-12.56632388004711</v>
       </c>
@@ -8810,12 +8204,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8854,7 +8242,6 @@
       <c r="J34" t="n">
         <v>0.2047</v>
       </c>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
         <v>-12.56632388004711</v>
       </c>
@@ -8869,12 +8256,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8913,7 +8294,6 @@
       <c r="J35" t="n">
         <v>0.2047</v>
       </c>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
         <v>-12.56632388004711</v>
       </c>
@@ -8928,12 +8308,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -8972,7 +8346,6 @@
       <c r="J36" t="n">
         <v>0.235</v>
       </c>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
         <v>-13.21480688116424</v>
       </c>
@@ -8987,16 +8360,12 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="n">
         <v>109.7217</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9035,7 +8404,6 @@
       <c r="J37" t="n">
         <v>0.235</v>
       </c>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
         <v>-13.21480688116424</v>
       </c>
@@ -9050,16 +8418,12 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="n">
         <v>109.7217</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -9098,7 +8462,6 @@
       <c r="J38" t="n">
         <v>0.235</v>
       </c>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
         <v>-13.21480688116424</v>
       </c>
@@ -9113,16 +8476,12 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="n">
         <v>109.7217</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9147,7 +8506,6 @@
       <c r="F39" t="n">
         <v>0.5409</v>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>8224</v>
       </c>
@@ -9157,7 +8515,6 @@
       <c r="J39" t="n">
         <v>0.235</v>
       </c>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
         <v>-13.21480688116424</v>
       </c>
@@ -9172,16 +8529,12 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
         <v>109.7217</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -9220,7 +8573,6 @@
       <c r="J40" t="n">
         <v>0.235</v>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
         <v>-13.21480688116424</v>
       </c>
@@ -9235,16 +8587,12 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="n">
         <v>109.7217</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9283,7 +8631,6 @@
       <c r="J41" t="n">
         <v>0.235</v>
       </c>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
         <v>-13.21480688116424</v>
       </c>
@@ -9298,16 +8645,12 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="n">
         <v>109.7217</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -9346,7 +8689,6 @@
       <c r="J42" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -9361,10 +8703,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
       <c r="T42" t="n">
         <v>1.5818</v>
       </c>
@@ -9409,7 +8747,6 @@
       <c r="J43" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -9424,10 +8761,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
       <c r="T43" t="n">
         <v>1.5818</v>
       </c>
@@ -9472,7 +8805,6 @@
       <c r="J44" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -9487,10 +8819,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
       <c r="T44" t="n">
         <v>1.5818</v>
       </c>
@@ -9521,7 +8849,6 @@
       <c r="F45" t="n">
         <v>0.3468</v>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>8220</v>
       </c>
@@ -9531,7 +8858,6 @@
       <c r="J45" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -9546,10 +8872,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
       <c r="T45" t="n">
         <v>1.5818</v>
       </c>
@@ -9594,7 +8916,6 @@
       <c r="J46" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -9609,10 +8930,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
       <c r="T46" t="n">
         <v>1.5818</v>
       </c>
@@ -9657,7 +8974,6 @@
       <c r="J47" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -9672,10 +8988,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
       <c r="T47" t="n">
         <v>1.5818</v>
       </c>
@@ -9720,7 +9032,6 @@
       <c r="J48" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -9735,10 +9046,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
       <c r="T48" t="n">
         <v>1.5818</v>
       </c>
@@ -9783,7 +9090,6 @@
       <c r="J49" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -9798,10 +9104,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
       <c r="T49" t="n">
         <v>1.5818</v>
       </c>
@@ -9846,7 +9148,6 @@
       <c r="J50" t="n">
         <v>0.2432</v>
       </c>
-      <c r="K50" t="inlineStr"/>
       <c r="L50" t="n">
         <v>-12.69000320699619</v>
       </c>
@@ -9861,10 +9162,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
       <c r="T50" t="n">
         <v>1.5818</v>
       </c>
@@ -9909,7 +9206,6 @@
       <c r="J51" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -9924,12 +9220,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -9968,7 +9258,6 @@
       <c r="J52" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -9983,12 +9272,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -10027,7 +9310,6 @@
       <c r="J53" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -10042,12 +9324,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -10072,7 +9348,6 @@
       <c r="F54" t="n">
         <v>0.2246</v>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>8220</v>
       </c>
@@ -10082,7 +9357,6 @@
       <c r="J54" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K54" t="inlineStr"/>
       <c r="L54" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -10097,12 +9371,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -10141,7 +9409,6 @@
       <c r="J55" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K55" t="inlineStr"/>
       <c r="L55" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -10156,12 +9423,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -10200,7 +9461,6 @@
       <c r="J56" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -10215,12 +9475,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -10259,7 +9513,6 @@
       <c r="J57" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -10274,12 +9527,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -10304,7 +9551,6 @@
       <c r="F58" t="n">
         <v>0.1254</v>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>8220</v>
       </c>
@@ -10314,7 +9560,6 @@
       <c r="J58" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K58" t="inlineStr"/>
       <c r="L58" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -10329,12 +9574,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -10359,7 +9598,6 @@
       <c r="F59" t="n">
         <v>0.1026</v>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>8220</v>
       </c>
@@ -10369,7 +9607,6 @@
       <c r="J59" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -10384,12 +9621,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -10428,7 +9659,6 @@
       <c r="J60" t="n">
         <v>0.2488</v>
       </c>
-      <c r="K60" t="inlineStr"/>
       <c r="L60" t="n">
         <v>-13.94548656674169</v>
       </c>
@@ -10443,12 +9673,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -10510,10 +9734,6 @@
       <c r="Q61" t="n">
         <v>1.48</v>
       </c>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -10575,10 +9795,6 @@
       <c r="Q62" t="n">
         <v>1.48</v>
       </c>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -10640,10 +9856,6 @@
       <c r="Q63" t="n">
         <v>1.48</v>
       </c>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -10705,10 +9917,6 @@
       <c r="Q64" t="n">
         <v>1.48</v>
       </c>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10733,7 +9941,6 @@
       <c r="F65" t="n">
         <v>0.2971</v>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>8220</v>
       </c>
@@ -10766,10 +9973,6 @@
       <c r="Q65" t="n">
         <v>1.48</v>
       </c>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -10831,10 +10034,6 @@
       <c r="Q66" t="n">
         <v>1.48</v>
       </c>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -10896,10 +10095,6 @@
       <c r="Q67" t="n">
         <v>1.48</v>
       </c>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10938,7 +10133,6 @@
       <c r="J68" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -10953,12 +10147,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -10983,7 +10171,6 @@
       <c r="F69" t="n">
         <v>0.1396</v>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>8220</v>
       </c>
@@ -10993,7 +10180,6 @@
       <c r="J69" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K69" t="inlineStr"/>
       <c r="L69" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -11008,12 +10194,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -11052,7 +10232,6 @@
       <c r="J70" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K70" t="inlineStr"/>
       <c r="L70" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -11067,12 +10246,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -11111,7 +10284,6 @@
       <c r="J71" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K71" t="inlineStr"/>
       <c r="L71" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -11126,12 +10298,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -11170,7 +10336,6 @@
       <c r="J72" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K72" t="inlineStr"/>
       <c r="L72" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -11185,12 +10350,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -11229,7 +10388,6 @@
       <c r="J73" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K73" t="inlineStr"/>
       <c r="L73" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -11244,12 +10402,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -11288,7 +10440,6 @@
       <c r="J74" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K74" t="inlineStr"/>
       <c r="L74" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -11303,12 +10454,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -11333,7 +10478,6 @@
       <c r="F75" t="n">
         <v>0.15</v>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>8220</v>
       </c>
@@ -11343,7 +10487,6 @@
       <c r="J75" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K75" t="inlineStr"/>
       <c r="L75" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -11358,12 +10501,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -11388,7 +10525,6 @@
       <c r="F76" t="n">
         <v>0.2115</v>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>8220</v>
       </c>
@@ -11398,7 +10534,6 @@
       <c r="J76" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K76" t="inlineStr"/>
       <c r="L76" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -11413,12 +10548,6 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -11457,7 +10586,6 @@
       <c r="J77" t="n">
         <v>0.6358</v>
       </c>
-      <c r="K77" t="inlineStr"/>
       <c r="L77" t="n">
         <v>-1.205510142681362</v>
       </c>
@@ -11472,14 +10600,83 @@
           <t>U or linear (b2&gt;=0)</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>P7_Capstone_JIBS — Embedded Figures (data-driven, source-traceable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Each figure below was rendered from a CSV / data file produced by the paper's Stata or R replication pipeline. Provenance is listed under each figure. See 'STATA_REPLICATION_GUIDE.md' (Vietnamese + English) for end-to-end reproduction instructions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Figure 1: figure_1_conceptual_model.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Provenance: scripts/render_conceptual_models.py → matplotlib (theoretical diagram, not data-driven)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Figure 2: figure_2_icrv_gradient.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Provenance: p7/replication/figures/ ← p7/replication/icrv_marginal_effects.csv (R 02_run_p7_models.py)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A34:H34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>